--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,126 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -690,97 +864,126 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -809,97 +1012,126 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.06542056074766354</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.008691384892873792</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -928,97 +1160,126 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1047,97 +1308,126 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -1166,97 +1456,126 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1285,97 +1604,126 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -1404,97 +1752,126 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0.1186440677966102</v>
-      </c>
       <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.004345692446436896</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1523,97 +1900,126 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1642,97 +2048,126 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="n">
-        <v>0.4516129032258064</v>
-      </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.003875939847584092</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -1761,97 +2196,126 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>0.2258064516129032</v>
-      </c>
       <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.004345692446436896</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1880,97 +2344,126 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="BA13" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="BB13" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -1999,97 +2492,126 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="BA14" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="BB14" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -2118,97 +2640,126 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
-        <v>0.2333333333333333</v>
-      </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.004345692446436896</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="AW15" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="BA15" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="BB15" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2237,97 +2788,126 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="AW16" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="BA16" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="BB16" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2356,97 +2936,126 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="AW17" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="BA17" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="BB17" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -2475,97 +3084,126 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>4</v>
       </c>
-      <c r="N18" t="n">
-        <v>0.9032258064516129</v>
-      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.01738276978574758</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="AW18" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="BA18" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="BB18" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2594,97 +3232,126 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="n">
-        <v>0.2333333333333333</v>
-      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.001937969923792046</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="BA19" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="BB19" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -2713,97 +3380,126 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
-        <v>0.2333333333333333</v>
-      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.004345692446436896</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="AW20" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="BA20" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="BB20" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -2832,97 +3528,126 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Endemic typhus fever</t>
+          <t>D169</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="AW21" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="BA21" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="BB21" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="BC21" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -3040,7 +3765,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3050,27 +3775,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3080,22 +3805,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1203,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1357,9 +1348,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1505,9 +1493,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1653,9 +1638,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1949,9 +1931,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2097,9 +2076,6 @@
       <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -2245,9 +2221,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -2393,9 +2366,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2541,9 +2511,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2689,9 +2656,6 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -2837,9 +2801,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2946,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3091,6 @@
       <c r="O18" t="n">
         <v>4</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.01738276978574758</v>
       </c>
@@ -3281,9 +3236,6 @@
       <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -3429,9 +3381,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -3575,9 +3524,6 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -3376,13 +3376,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -13436,12 +13436,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -13475,13 +13475,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -13514,42 +13514,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13581,12 +13581,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -13620,13 +13620,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -13659,42 +13659,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13726,12 +13726,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -13765,93 +13765,81 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
-      </c>
-      <c r="P73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13866,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13930,98 +13918,18 @@
       <c r="P74" t="n">
         <v>3</v>
       </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R74" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN74" t="b">
-        <v>1</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -14115,7 +14023,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14150,7 +14058,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -14159,26 +14067,106 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P75" t="n">
-        <v>7</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0.1185286028567933</v>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -14272,7 +14260,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14324,98 +14312,18 @@
       <c r="P76" t="n">
         <v>7</v>
       </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R76" t="n">
+        <v>0.1185286028567933</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN76" t="b">
-        <v>1</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -14509,7 +14417,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14544,7 +14452,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -14553,26 +14461,106 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>7</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -14666,7 +14654,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14718,98 +14706,18 @@
       <c r="P78" t="n">
         <v>0</v>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG78" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN78" t="b">
-        <v>1</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -14903,7 +14811,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14938,7 +14846,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -14947,26 +14855,106 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>2</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -15060,7 +15048,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15112,98 +15100,18 @@
       <c r="P80" t="n">
         <v>2</v>
       </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R80" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG80" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN80" t="b">
-        <v>1</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -15297,17 +15205,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -15332,90 +15240,182 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -15447,12 +15447,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -15486,93 +15486,81 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>3</v>
-      </c>
-      <c r="P82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.05079797265291142</v>
+        <v>0</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15587,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15651,98 +15639,18 @@
       <c r="P83" t="n">
         <v>3</v>
       </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R83" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD83" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG83" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN83" t="b">
-        <v>1</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -15836,7 +15744,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15871,7 +15779,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -15880,26 +15788,106 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P84" t="n">
-        <v>5</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0.08466328775485238</v>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>1</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -15993,7 +15981,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16045,98 +16033,18 @@
       <c r="P85" t="n">
         <v>5</v>
       </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R85" t="n">
+        <v>0.08466328775485238</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN85" t="b">
-        <v>1</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -16230,7 +16138,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16265,7 +16173,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -16274,26 +16182,106 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>5</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>1</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -16387,7 +16375,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16439,98 +16427,18 @@
       <c r="P87" t="n">
         <v>0</v>
       </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN87" t="b">
-        <v>1</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -16596,6 +16504,243 @@
         </is>
       </c>
       <c r="BC87" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -16717,7 +16862,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -16727,7 +16872,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -16746,6 +16746,545 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>2</v>
+      </c>
+      <c r="O89" t="n">
+        <v>2</v>
+      </c>
+      <c r="P89" t="n">
+        <v>2</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>2</v>
+      </c>
+      <c r="P90" t="n">
+        <v>2</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16779,7 +17318,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -16862,7 +17401,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -16872,7 +17411,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -16892,7 +17431,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -16924,7 +17463,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
